--- a/reports/Debug-snowbowl-20260105/For Winter Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260105/For Winter Ending (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -70,22 +70,16 @@
     <t>account</t>
   </si>
   <si>
-    <t>T257</t>
-  </si>
-  <si>
-    <t>T121</t>
+    <t>T104</t>
+  </si>
+  <si>
+    <t>T103</t>
   </si>
   <si>
     <t>T101</t>
   </si>
   <si>
-    <t>T103</t>
-  </si>
-  <si>
     <t>T100</t>
-  </si>
-  <si>
-    <t>T104</t>
   </si>
   <si>
     <t>department</t>
@@ -502,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -518,18 +512,22 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="D2" s="2">
-        <v>6549.74</v>
+        <v>127248.78</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -540,10 +538,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>48.00</v>
+        <v>662.30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -554,10 +552,10 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2">
-        <v>124089.60</v>
+        <v>91036.54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -568,10 +566,10 @@
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2">
-        <v>2421281.87</v>
+        <v>55420.77</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -582,230 +580,190 @@
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2">
-        <v>227479.30</v>
+        <v>1262059.33</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2">
-        <v>4222320.37</v>
+        <v>407099.16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="2">
-        <v>1289.05</v>
+        <v>1074266.93</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2">
-        <v>460763.31</v>
+        <v>51128.39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2">
-        <v>637601.89</v>
+        <v>365835.91</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2">
-        <v>1484376.79</v>
+        <v>1304.99</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2">
-        <v>65311.26</v>
+        <v>335.50</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2">
-        <v>516509.03</v>
+        <v>424356.83</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2">
-        <v>1304.99</v>
+        <v>547504.49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2">
-        <v>348.52</v>
+        <v>53732.94</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2">
-        <v>467299.93</v>
+        <v>32074.31</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="2">
-        <v>694567.20</v>
+        <v>14447.95</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="2">
-        <v>66908.99</v>
+        <v>147632.81</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2">
-        <v>36542.95</v>
+        <v>23192.44</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" s="2">
-        <v>14447.95</v>
+        <v>3808.00</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2">
-        <v>156291.65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="2">
-        <v>23192.44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="2">
-        <v>3808.00</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="2">
-        <v>41550.63</v>
+        <v>21460.63</v>
       </c>
     </row>
   </sheetData>
